--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484753_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484753_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1716</v>
+        <v>2.6313</v>
       </c>
       <c r="E2" t="n">
-        <v>3.641</v>
+        <v>4.8891</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4694</v>
+        <v>-2.2578</v>
       </c>
       <c r="G2" t="n">
         <v>1.2657</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2263</v>
+        <v>0.2335</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9159</v>
+        <v>0.3322</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3103</v>
+        <v>-0.0987</v>
       </c>
       <c r="V2" t="n">
         <v>0.9434</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>J. ARTIGUES DAÑOBEITIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4249</v>
+        <v>0.317</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1764</v>
+        <v>0.317</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.7515</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.0218</v>
+        <v>0.317</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2488</v>
+        <v>0.317</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.2707</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9007</v>
+        <v>0.317</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7688</v>
+        <v>0.317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1319</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.9225</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.5199</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.4026</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5789</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9175</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3386</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DAÑOBEITIA</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.317</v>
+        <v>-0.2996</v>
       </c>
       <c r="E4" t="n">
-        <v>0.317</v>
+        <v>3.3196</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-3.6192</v>
       </c>
       <c r="G4" t="n">
-        <v>0.317</v>
+        <v>-2.0218</v>
       </c>
       <c r="H4" t="n">
-        <v>0.317</v>
+        <v>0.2488</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-2.2707</v>
       </c>
       <c r="J4" t="n">
-        <v>0.317</v>
+        <v>2.9007</v>
       </c>
       <c r="K4" t="n">
-        <v>0.317</v>
+        <v>2.7688</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.1319</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-4.9225</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-2.5199</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-2.4026</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.8544</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.0607</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.2063</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-1.4555</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8415</v>
+        <v>1.1208</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4175</v>
+        <v>-2.5763</v>
       </c>
       <c r="G5" t="n">
         <v>-1.7867</v>
@@ -844,13 +844,13 @@
         <v>0.5661</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2862</v>
+        <v>0.4068</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2556</v>
+        <v>0.5349</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0306</v>
+        <v>-0.1281</v>
       </c>
       <c r="V5" t="n">
         <v>0.3018</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3115</v>
+        <v>-1.4901</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3728</v>
+        <v>2.4059</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.6843</v>
+        <v>-3.896</v>
       </c>
       <c r="G6" t="n">
         <v>-2.5573</v>
@@ -922,13 +922,13 @@
         <v>0.7548</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5091</v>
+        <v>0.3124</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9871</v>
+        <v>0.0461</v>
       </c>
       <c r="U6" t="n">
-        <v>0.478</v>
+        <v>0.2664</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.2534</v>
+        <v>-3.1069</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7269</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5265</v>
+        <v>-2.3413</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9923</v>
@@ -1000,13 +1000,13 @@
         <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0159</v>
+        <v>0.1306</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1365</v>
+        <v>-0.1751</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1206</v>
+        <v>0.3057</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2452</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.3687</v>
+        <v>-3.5305</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3025</v>
+        <v>1.1407</v>
       </c>
       <c r="F8" t="n">
         <v>-4.6712</v>
@@ -1078,10 +1078,10 @@
         <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3651</v>
+        <v>0.4732</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5291</v>
+        <v>0.3092</v>
       </c>
       <c r="U8" t="n">
         <v>0.164</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.6697</v>
+        <v>-5.5315</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7077</v>
+        <v>-0.6489</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.962</v>
+        <v>-4.8826</v>
       </c>
       <c r="G9" t="n">
         <v>-3.867</v>
@@ -1156,13 +1156,13 @@
         <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6896</v>
+        <v>-0.5514</v>
       </c>
       <c r="T9" t="n">
-        <v>0.074</v>
+        <v>0.1328</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.6842</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9244</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9337</v>
+        <v>-5.5515</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9176</v>
+        <v>-4.8575</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0162</v>
+        <v>-0.694</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3533</v>
+        <v>-1.8917</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3901</v>
+        <v>-0.3052</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9632</v>
+        <v>-1.5865</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8236</v>
+        <v>-0.2773</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8124</v>
+        <v>0.2488</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0112</v>
+        <v>-0.5262</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5297</v>
+        <v>-1.6144</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5777</v>
+        <v>-0.5541</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.952</v>
+        <v>-1.0603</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.2079</v>
+        <v>-3.5853</v>
       </c>
       <c r="Q10" t="n">
         <v>-4.7175</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2121</v>
+        <v>0.2273</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6235</v>
+        <v>0.1373</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5885</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5846</v>
+        <v>-0.3018</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5846</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9781</v>
+        <v>-7.2789</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0725</v>
+        <v>-5.813</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9056</v>
+        <v>-1.4659</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8917</v>
+        <v>-4.3533</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3052</v>
+        <v>-2.3901</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5865</v>
+        <v>-1.9632</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2773</v>
+        <v>-1.8236</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2488</v>
+        <v>-0.8124</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5262</v>
+        <v>-1.0112</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6144</v>
+        <v>-2.5297</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5541</v>
+        <v>-1.5777</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0603</v>
+        <v>-0.952</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.5853</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.7175</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1993</v>
+        <v>0.8669</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.7281</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1216</v>
+        <v>0.1388</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3018</v>
+        <v>-0.5846</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3018</v>
+        <v>-0.5846</v>
       </c>
     </row>
     <row r="12">
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-26.1777</v>
+        <v>-25.2962</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2264999999999997</v>
+        <v>1.108099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-26.4042</v>
+        <v>-26.4043</v>
       </c>
       <c r="G12" t="n">
         <v>-19.8346</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.387899999999999</v>
+        <v>-7.3879</v>
       </c>
       <c r="I12" t="n">
         <v>-12.4468</v>
@@ -1366,10 +1366,10 @@
         <v>8.758699999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6485</v>
+        <v>4.648499999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>4.1102</v>
+        <v>4.110199999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-28.5933</v>
@@ -1390,13 +1390,13 @@
         <v>8.4915</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0719</v>
+        <v>2.9537</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2243</v>
+        <v>3.1062</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1523999999999999</v>
+        <v>-0.1524</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8108</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.1439</v>
+        <v>13.8519</v>
       </c>
       <c r="E13" t="n">
-        <v>11.3795</v>
+        <v>12.3539</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7644</v>
+        <v>1.4981</v>
       </c>
       <c r="G13" t="n">
         <v>9.2059</v>
@@ -1468,13 +1468,13 @@
         <v>2.4531</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3073</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3521</v>
+        <v>-0.3778</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9552</v>
+        <v>-0.2215</v>
       </c>
       <c r="V13" t="n">
         <v>2.7922</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.6728</v>
+        <v>9.561500000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>8.9222</v>
+        <v>7.9479</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7506</v>
+        <v>1.6136</v>
       </c>
       <c r="G14" t="n">
         <v>6.1018</v>
@@ -1546,13 +1546,13 @@
         <v>2.6418</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3256</v>
+        <v>0.2143</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3049</v>
+        <v>0.3306</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0207</v>
+        <v>-0.1163</v>
       </c>
       <c r="V14" t="n">
         <v>0.6036</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0824</v>
+        <v>6.5892</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6964</v>
+        <v>4.9169</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3859</v>
+        <v>1.6722</v>
       </c>
       <c r="G15" t="n">
         <v>2.6457</v>
@@ -1624,13 +1624,13 @@
         <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4931</v>
+        <v>0.9999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5495</v>
+        <v>0.77</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0564</v>
+        <v>0.2299</v>
       </c>
       <c r="V15" t="n">
         <v>1.2452</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1375</v>
+        <v>2.4304</v>
       </c>
       <c r="E16" t="n">
-        <v>3.192</v>
+        <v>2.8022</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0544</v>
+        <v>-0.3719</v>
       </c>
       <c r="G16" t="n">
         <v>1.7445</v>
@@ -1702,13 +1702,13 @@
         <v>0.5661</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4497</v>
+        <v>0.7425</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0763</v>
+        <v>0.6866</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3733</v>
+        <v>0.0559</v>
       </c>
       <c r="V16" t="n">
         <v>0.3208</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. FONT FENOLLAR</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2614</v>
+        <v>1.8818</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5713</v>
+        <v>0.456</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3099</v>
+        <v>1.4258</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3972</v>
+        <v>-0.0554</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.709</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5066000000000001</v>
+        <v>-0.7644</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6301</v>
+        <v>1.6203</v>
       </c>
       <c r="K17" t="n">
-        <v>0.972</v>
+        <v>1.8657</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6581</v>
+        <v>-0.2453</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2329</v>
+        <v>-1.6758</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0814</v>
+        <v>-1.1566</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1515</v>
+        <v>-0.5191</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.0192</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1358</v>
+        <v>-0.1005</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0588</v>
+        <v>-0.1829</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.077</v>
+        <v>0.0824</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>G. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0494</v>
+        <v>1.3408</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0663</v>
+        <v>1.5713</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9832</v>
+        <v>-0.2305</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0554</v>
+        <v>1.3972</v>
       </c>
       <c r="H18" t="n">
-        <v>0.709</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7644</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6203</v>
+        <v>1.6301</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8657</v>
+        <v>0.972</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2453</v>
+        <v>0.6581</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6758</v>
+        <v>-0.2329</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1566</v>
+        <v>-0.0814</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5191</v>
+        <v>-0.1515</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.0192</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9329</v>
+        <v>-0.0564</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5726</v>
+        <v>-0.0588</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3603</v>
+        <v>0.0024</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.038</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.038</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5817</v>
+        <v>0.7478</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3658</v>
+        <v>-0.1709</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9475</v>
+        <v>0.9187</v>
       </c>
       <c r="G19" t="n">
         <v>0.2884</v>
@@ -1936,13 +1936,13 @@
         <v>0.3774</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4703</v>
+        <v>-0.2754</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3863</v>
+        <v>0.3574</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7502</v>
+        <v>-0.8031</v>
       </c>
       <c r="E20" t="n">
         <v>-0.6461</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1041</v>
+        <v>-0.157</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8202</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0171</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1288</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5388</v>
+        <v>-2.3008</v>
       </c>
       <c r="E21" t="n">
         <v>0.5716</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1105</v>
+        <v>-2.8724</v>
       </c>
       <c r="G21" t="n">
         <v>1.7386</v>
@@ -2092,13 +2092,13 @@
         <v>1.887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8436</v>
+        <v>-0.6055</v>
       </c>
       <c r="T21" t="n">
         <v>0.0152</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8588</v>
+        <v>-0.6207</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4904</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0041</v>
+        <v>-2.5114</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3342</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3384</v>
+        <v>-3.1379</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6785</v>
@@ -2170,13 +2170,13 @@
         <v>1.3209</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0804</v>
+        <v>-0.5877</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5755</v>
+        <v>-0.2832</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5049</v>
+        <v>-0.3045</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6226</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4581</v>
+        <v>-2.6173</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3173</v>
+        <v>-4.025</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8593</v>
+        <v>1.4077</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7334000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>1.1322</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0264</v>
+        <v>-0.1856</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7055</v>
+        <v>-0.4131</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3209</v>
+        <v>0.2275</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>26.17789999999999</v>
+        <v>28.1708</v>
       </c>
       <c r="E24" t="n">
         <v>26.4043</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2264000000000002</v>
+        <v>1.7664</v>
       </c>
       <c r="G24" t="n">
         <v>19.8346</v>
@@ -2326,13 +2326,13 @@
         <v>15.096</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.072</v>
+        <v>-0.07920000000000016</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1523</v>
+        <v>0.1523999999999998</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.2244</v>
+        <v>-0.2317</v>
       </c>
       <c r="V24" t="n">
         <v>1.8108</v>
